--- a/stock/gold/2026.xlsx
+++ b/stock/gold/2026.xlsx
@@ -16,12 +16,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="98">
   <si>
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="Arial Unicode MS"/>
         <charset val="134"/>
       </rPr>
@@ -31,7 +30,6 @@
       <rPr>
         <b/>
         <sz val="14"/>
-        <color rgb="FF000000"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
@@ -45,7 +43,6 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="Arial Unicode MS"/>
         <charset val="134"/>
       </rPr>
@@ -54,7 +51,6 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="仿宋_GB2312"/>
         <charset val="134"/>
       </rPr>
@@ -63,7 +59,6 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
         <charset val="134"/>
       </rPr>
@@ -80,7 +75,6 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="Arial Unicode MS"/>
         <charset val="134"/>
       </rPr>
@@ -89,7 +83,6 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF000000"/>
         <rFont val="Tahoma"/>
         <charset val="134"/>
       </rPr>
@@ -104,12 +97,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <charset val="134"/>
-      </rPr>
       <t>1.</t>
     </r>
     <r>
@@ -150,16 +137,28 @@
     <t>24639.84 </t>
   </si>
   <si>
+    <t>34105.47 </t>
+  </si>
+  <si>
+    <t>24857.91 </t>
+  </si>
+  <si>
+    <t>34422.38 </t>
+  </si>
+  <si>
+    <t>25148.72 </t>
+  </si>
+  <si>
+    <t>34162.62 </t>
+  </si>
+  <si>
+    <t>25191.76 </t>
+  </si>
+  <si>
     <t>       Foreign currency reserves </t>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <charset val="134"/>
-      </rPr>
       <t>2.</t>
     </r>
     <r>
@@ -200,16 +199,28 @@
     <t>80.38 </t>
   </si>
   <si>
+    <t>109.38 </t>
+  </si>
+  <si>
+    <t>79.72 </t>
+  </si>
+  <si>
+    <t>111.85 </t>
+  </si>
+  <si>
+    <t>81.72 </t>
+  </si>
+  <si>
+    <t>109.81 </t>
+  </si>
+  <si>
+    <t>80.97 </t>
+  </si>
+  <si>
     <t>       IMF reserve position</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <charset val="134"/>
-      </rPr>
       <t>3.</t>
     </r>
     <r>
@@ -247,16 +258,28 @@
     <t>553.43 </t>
   </si>
   <si>
+    <t>560.33 </t>
+  </si>
+  <si>
+    <t>408.40 </t>
+  </si>
+  <si>
+    <t>560.34 </t>
+  </si>
+  <si>
+    <t>409.38 </t>
+  </si>
+  <si>
+    <t>551.42 </t>
+  </si>
+  <si>
+    <t>406.62 </t>
+  </si>
+  <si>
     <t>       SDRs</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <charset val="134"/>
-      </rPr>
       <t>4.</t>
     </r>
     <r>
@@ -297,6 +320,24 @@
     <t>2527.02 </t>
   </si>
   <si>
+    <t>3441.72 </t>
+  </si>
+  <si>
+    <t>2508.51 </t>
+  </si>
+  <si>
+    <t>3407.52 </t>
+  </si>
+  <si>
+    <t>2489.51 </t>
+  </si>
+  <si>
+    <t>3037.24 </t>
+  </si>
+  <si>
+    <t>2239.68 </t>
+  </si>
+  <si>
     <t>       Gold </t>
   </si>
   <si>
@@ -309,13 +350,16 @@
     <t>7438万盎司</t>
   </si>
   <si>
+    <t>7464万盎司</t>
+  </si>
+  <si>
+    <t>7496万盎司</t>
+  </si>
+  <si>
+    <t>7544万盎司</t>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <charset val="134"/>
-      </rPr>
       <t>5.</t>
     </r>
     <r>
@@ -365,16 +409,28 @@
     <t>-0.07 </t>
   </si>
   <si>
+    <t>0.27 </t>
+  </si>
+  <si>
+    <t>0.20 </t>
+  </si>
+  <si>
+    <t>3.77 </t>
+  </si>
+  <si>
+    <t>2.75 </t>
+  </si>
+  <si>
+    <t>2.09 </t>
+  </si>
+  <si>
+    <t>1.54 </t>
+  </si>
+  <si>
     <t>      Other reserve assets </t>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial Unicode MS"/>
-        <charset val="134"/>
-      </rPr>
       <t>    </t>
     </r>
     <r>
@@ -406,10 +462,28 @@
     <t>27655.19 </t>
   </si>
   <si>
+    <t>38217.17 </t>
+  </si>
+  <si>
+    <t>27854.74 </t>
+  </si>
+  <si>
+    <t>38505.86 </t>
+  </si>
+  <si>
+    <t>28132.08 </t>
+  </si>
+  <si>
+    <t>37863.18 </t>
+  </si>
+  <si>
+    <t>27920.57 </t>
+  </si>
+  <si>
     <t>      Total</t>
   </si>
   <si>
-    <t>   注：自2016年4月1日起，除按美元公布官方储备资产外，增加以国际货币基金组织特别提款权（SDR）公布相关数据，折算汇率来源于国际货币基金组织网站，其中2026年1月USD/SDR=0.723657，2026年2月USD/SDR=0.727397，2026年3月USD/SDR=0.737251。</t>
+    <t>   注：自2016年4月1日起，除按美元公布官方储备资产外，增加以国际货币基金组织特别提款权（SDR）公布相关数据，折算汇率来源于国际货币基金组织网站，其中2026年1月USD/SDR=0.723657，2026年2月USD/SDR=0.727397，2026年3月USD/SDR=0.737251，2026年4月USD/SDR=0.728854，2026年5月USD/SDR=0.730592，2026年6月USD/SDR=0.737407。</t>
   </si>
 </sst>
 </file>
@@ -422,13 +496,34 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Unicode MS"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -437,8 +532,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Tahoma"/>
       <charset val="134"/>
@@ -450,92 +544,116 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
+      <u/>
+      <sz val="11"/>
+      <color indexed="4"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color indexed="20"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="65"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <color indexed="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -543,67 +661,34 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="宋体"/>
+      <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="仿宋_GB2312"/>
       <charset val="134"/>
     </font>
     <font>
@@ -622,204 +707,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF99CCFF"/>
-        <bgColor indexed="64"/>
+        <fgColor indexed="44"/>
+        <bgColor indexed="44"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
-        <bgColor indexed="64"/>
+        <fgColor indexed="43"/>
+        <bgColor indexed="43"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <bgColor theme="9" tint="0.599993896298105"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor theme="7" tint="0.599993896298105"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor theme="5" tint="0.599993896298105"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor theme="8" tint="0.599993896298105"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <bgColor theme="4" tint="0.599993896298105"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFA5A5A5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <bgColor theme="6" tint="0.599993896298105"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor theme="9" tint="0.399975585192419"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor theme="7" tint="0.399975585192419"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor theme="5" tint="0.399975585192419"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="47"/>
+        <bgColor indexed="47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor theme="4" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor theme="8" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor theme="6" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor theme="8" tint="0.399975585192419"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor theme="4" tint="0.399975585192419"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor theme="6" tint="0.399975585192419"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="26"/>
+        <bgColor indexed="26"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
+        <bgColor theme="9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7"/>
+        <bgColor theme="7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
+        <bgColor theme="5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor theme="7" tint="0.799981688894314"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor theme="5" tint="0.799981688894314"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
+        <bgColor theme="9" tint="0.799981688894314"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="16">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -830,10 +915,10 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -841,13 +926,33 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -884,10 +989,10 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -896,7 +1001,7 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -921,6 +1026,30 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -974,182 +1103,158 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="12" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="15" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="14" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="12" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="10" applyNumberFormat="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1176,28 +1281,31 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1206,14 +1314,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1320,73 +1425,13 @@
     <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Cambria"/>
+        <a:cs typeface="Arial"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="等线"/>
+        <a:ea typeface="等线"/>
+        <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1394,7 +1439,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1417,7 +1462,7 @@
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1491,24 +1536,13 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1530,11 +1564,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
+          <a:path path="circle"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1549,9 +1581,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:path path="circle"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1657,7 +1687,7 @@
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
     </row>
-    <row r="4" customHeight="1" spans="1:25">
+    <row r="4" spans="1:25">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -1697,18 +1727,18 @@
         <v>2026.09</v>
       </c>
       <c r="S4" s="5"/>
-      <c r="T4" s="21" t="s">
+      <c r="T4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="U4" s="5"/>
+      <c r="U4" s="16"/>
       <c r="V4" s="5">
         <v>2026.11</v>
       </c>
       <c r="W4" s="5"/>
-      <c r="X4" s="16">
+      <c r="X4" s="17">
         <v>2026.12</v>
       </c>
-      <c r="Y4" s="16"/>
+      <c r="Y4" s="17"/>
     </row>
     <row r="5" customHeight="1" spans="1:25">
       <c r="A5" s="4"/>
@@ -1781,7 +1811,7 @@
       <c r="X5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Y5" s="17" t="s">
+      <c r="Y5" s="18" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1856,7 +1886,7 @@
       <c r="X6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="Y6" s="18" t="s">
+      <c r="Y6" s="19" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1885,7 +1915,7 @@
       <c r="V7" s="8"/>
       <c r="W7" s="8"/>
       <c r="X7" s="8"/>
-      <c r="Y7" s="19"/>
+      <c r="Y7" s="20"/>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:25">
       <c r="A8" s="9" t="s">
@@ -1909,12 +1939,24 @@
       <c r="G8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
+      <c r="H8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="N8" s="10"/>
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
@@ -1926,11 +1968,11 @@
       <c r="V8" s="10"/>
       <c r="W8" s="10"/>
       <c r="X8" s="10"/>
-      <c r="Y8" s="20"/>
+      <c r="Y8" s="21"/>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:25">
       <c r="A9" s="11" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
@@ -1955,36 +1997,48 @@
       <c r="V9" s="10"/>
       <c r="W9" s="10"/>
       <c r="X9" s="10"/>
-      <c r="Y9" s="20"/>
+      <c r="Y9" s="21"/>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:25">
       <c r="A10" s="9" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
+        <v>28</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>34</v>
+      </c>
       <c r="N10" s="10"/>
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
@@ -1996,11 +2050,11 @@
       <c r="V10" s="10"/>
       <c r="W10" s="10"/>
       <c r="X10" s="10"/>
-      <c r="Y10" s="20"/>
+      <c r="Y10" s="21"/>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:25">
       <c r="A11" s="11" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -2025,36 +2079,48 @@
       <c r="V11" s="10"/>
       <c r="W11" s="10"/>
       <c r="X11" s="10"/>
-      <c r="Y11" s="20"/>
+      <c r="Y11" s="21"/>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:25">
       <c r="A12" s="9" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
+        <v>40</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>47</v>
+      </c>
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
@@ -2066,11 +2132,11 @@
       <c r="V12" s="10"/>
       <c r="W12" s="10"/>
       <c r="X12" s="10"/>
-      <c r="Y12" s="20"/>
+      <c r="Y12" s="21"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:25">
       <c r="A13" s="11" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
@@ -2095,36 +2161,48 @@
       <c r="V13" s="10"/>
       <c r="W13" s="10"/>
       <c r="X13" s="10"/>
-      <c r="Y13" s="20"/>
+      <c r="Y13" s="21"/>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:25">
       <c r="A14" s="9" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
+        <v>55</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>61</v>
+      </c>
       <c r="N14" s="10"/>
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
@@ -2136,11 +2214,11 @@
       <c r="V14" s="10"/>
       <c r="W14" s="10"/>
       <c r="X14" s="10"/>
-      <c r="Y14" s="20"/>
+      <c r="Y14" s="21"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:25">
       <c r="A15" s="11" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
@@ -2165,34 +2243,46 @@
       <c r="V15" s="10"/>
       <c r="W15" s="10"/>
       <c r="X15" s="10"/>
-      <c r="Y15" s="20"/>
+      <c r="Y15" s="21"/>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:25">
       <c r="A16" s="12"/>
       <c r="B16" s="10" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
+        <v>65</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>68</v>
+      </c>
       <c r="N16" s="10"/>
       <c r="O16" s="10"/>
       <c r="P16" s="10"/>
@@ -2204,36 +2294,48 @@
       <c r="V16" s="10"/>
       <c r="W16" s="10"/>
       <c r="X16" s="10"/>
-      <c r="Y16" s="20"/>
+      <c r="Y16" s="21"/>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:25">
       <c r="A17" s="9" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
+        <v>75</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>81</v>
+      </c>
       <c r="N17" s="10"/>
       <c r="O17" s="10"/>
       <c r="P17" s="10"/>
@@ -2245,11 +2347,11 @@
       <c r="V17" s="10"/>
       <c r="W17" s="10"/>
       <c r="X17" s="10"/>
-      <c r="Y17" s="20"/>
+      <c r="Y17" s="21"/>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:25">
       <c r="A18" s="11" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
@@ -2274,52 +2376,64 @@
       <c r="V18" s="10"/>
       <c r="W18" s="10"/>
       <c r="X18" s="10"/>
-      <c r="Y18" s="20"/>
+      <c r="Y18" s="21"/>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:25">
       <c r="A19" s="9" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
+        <v>89</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>95</v>
+      </c>
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
       <c r="P19" s="13"/>
       <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
-      <c r="U19" s="13"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="13"/>
-      <c r="X19" s="13"/>
-      <c r="Y19" s="20"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="21"/>
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:25">
       <c r="A20" s="14" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
@@ -2337,18 +2451,18 @@
       <c r="O20" s="13"/>
       <c r="P20" s="13"/>
       <c r="Q20" s="13"/>
-      <c r="R20" s="13"/>
-      <c r="S20" s="13"/>
-      <c r="T20" s="13"/>
-      <c r="U20" s="13"/>
-      <c r="V20" s="13"/>
-      <c r="W20" s="13"/>
-      <c r="X20" s="13"/>
-      <c r="Y20" s="20"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="21"/>
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:25">
       <c r="A21" s="15" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
@@ -2375,7 +2489,7 @@
       <c r="X21" s="15"/>
       <c r="Y21" s="15"/>
     </row>
-    <row r="22" customHeight="1" spans="1:25">
+    <row r="22" spans="1:25">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -2402,7 +2516,7 @@
       <c r="X22" s="3"/>
       <c r="Y22" s="3"/>
     </row>
-    <row r="23" customHeight="1" spans="1:25">
+    <row r="23" spans="1:25">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -2429,7 +2543,7 @@
       <c r="X23" s="3"/>
       <c r="Y23" s="3"/>
     </row>
-    <row r="24" customHeight="1" spans="1:25">
+    <row r="24" spans="1:25">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -2456,7 +2570,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
     </row>
-    <row r="25" customHeight="1" spans="1:25">
+    <row r="25" spans="1:25">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2483,7 +2597,7 @@
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
     </row>
-    <row r="26" customHeight="1" spans="1:25">
+    <row r="26" spans="1:25">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -2510,7 +2624,7 @@
       <c r="X26" s="3"/>
       <c r="Y26" s="3"/>
     </row>
-    <row r="27" customHeight="1" spans="1:25">
+    <row r="27" spans="1:25">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -2537,7 +2651,7 @@
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
     </row>
-    <row r="28" customHeight="1" spans="1:25">
+    <row r="28" spans="1:25">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -2564,7 +2678,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
     </row>
-    <row r="29" customHeight="1" spans="1:25">
+    <row r="29" spans="1:25">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -2591,7 +2705,7 @@
       <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
     </row>
-    <row r="30" customHeight="1" spans="1:25">
+    <row r="30" spans="1:25">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -2618,7 +2732,7 @@
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
     </row>
-    <row r="31" customHeight="1" spans="1:25">
+    <row r="31" spans="1:25">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -2645,7 +2759,7 @@
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
     </row>
-    <row r="32" customHeight="1" spans="1:25">
+    <row r="32" spans="1:25">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2672,7 +2786,7 @@
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
     </row>
-    <row r="33" customHeight="1" spans="1:25">
+    <row r="33" spans="1:25">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -2699,7 +2813,7 @@
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
     </row>
-    <row r="34" customHeight="1" spans="1:25">
+    <row r="34" spans="1:25">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -2726,7 +2840,7 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
-    <row r="35" customHeight="1" spans="1:25">
+    <row r="35" spans="1:25">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -2753,7 +2867,7 @@
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
     </row>
-    <row r="36" customHeight="1" spans="1:25">
+    <row r="36" spans="1:25">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2780,7 +2894,7 @@
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
     </row>
-    <row r="37" customHeight="1" spans="1:25">
+    <row r="37" spans="1:25">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2807,7 +2921,7 @@
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
     </row>
-    <row r="38" customHeight="1" spans="1:25">
+    <row r="38" spans="1:25">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -2834,7 +2948,7 @@
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
     </row>
-    <row r="39" customHeight="1" spans="1:25">
+    <row r="39" spans="1:25">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2861,7 +2975,7 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
     </row>
-    <row r="40" customHeight="1" spans="1:25">
+    <row r="40" spans="1:25">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -3072,7 +3186,7 @@
     <mergeCell ref="Y19:Y20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="51" fitToHeight="0" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="51" fitToHeight="0" orientation="landscape" horizontalDpi="600" verticalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -3084,7 +3198,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -3096,7 +3210,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600"/>
   <headerFooter/>
 </worksheet>
 </file>